--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260903.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260903.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>66,388,766</t>
+          <t>139,185,084</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>139,185,084</t>
+          <t>158,860,485</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>158,860,485</t>
+          <t>66,388,766</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>57,500,636</t>
+          <t>121,803,583</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>121,803,583</t>
+          <t>57,500,636</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
